--- a/worked_examples/AIHE-CASE09B_upstream_model_provider_change_during_vendor_contract/workbook/xlsx/AIHE-CASE09B_worked_example_and_template.xlsx
+++ b/worked_examples/AIHE-CASE09B_upstream_model_provider_change_during_vendor_contract/workbook/xlsx/AIHE-CASE09B_worked_example_and_template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Raddd0def5b2e4cb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" r:id="Re3fefed711644ed9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="3" r:id="R5a9731d69def43cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rd0ee7a843174440a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" r:id="R662113866a8a4c52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="3" r:id="R30682d19d06e42b7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43,7 +43,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -60,6 +60,16 @@
         <x:fgColor rgb="FF2F5597"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF303236"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2230"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -68,7 +78,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -113,6 +123,16 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -323,12 +343,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="24" t="str">
         <x:v>AIHE-CASE09B - Upstream Model-Provider Change During a Vendor Contract</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
+      <x:c r="B1" s="24"/>
+      <x:c r="C1" s="24"/>
+      <x:c r="D1" s="24"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="8" t="str">
@@ -426,25 +446,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="12" t="str">
+      <x:c r="A1" s="25" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B1" s="12" t="str">
+      <x:c r="B1" s="25" t="str">
         <x:v>Baseline / current service</x:v>
       </x:c>
-      <x:c r="C1" s="12" t="str">
+      <x:c r="C1" s="25" t="str">
         <x:v>Option / intervention</x:v>
       </x:c>
-      <x:c r="D1" s="12" t="str">
+      <x:c r="D1" s="25" t="str">
         <x:v>Unit</x:v>
       </x:c>
-      <x:c r="E1" s="12" t="str">
+      <x:c r="E1" s="25" t="str">
         <x:v>Evidence source</x:v>
       </x:c>
-      <x:c r="F1" s="12" t="str">
+      <x:c r="F1" s="25" t="str">
         <x:v>Uncertainty or limitation</x:v>
       </x:c>
-      <x:c r="G1" s="12" t="str">
+      <x:c r="G1" s="25" t="str">
         <x:v>Owner</x:v>
       </x:c>
     </x:row>
@@ -611,24 +631,24 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="17" t="str">
+      <x:c r="A1" s="26" t="str">
         <x:v>Decision record</x:v>
       </x:c>
-      <x:c r="B1" s="17"/>
-      <x:c r="C1" s="17"/>
-      <x:c r="D1" s="17"/>
+      <x:c r="B1" s="26"/>
+      <x:c r="C1" s="26"/>
+      <x:c r="D1" s="26"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="25" t="str">
         <x:v>Decision field</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="25" t="str">
         <x:v>Response</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="25" t="str">
         <x:v>Owner / authority</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="25" t="str">
         <x:v>Date or review</x:v>
       </x:c>
     </x:row>
